--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -516,6 +516,39 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>vii rebirth nintendo</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>$45.49</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -549,6 +549,39 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>bowman basketball factory</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>$82.83</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -582,6 +582,39 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>nugget ice makers</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>$156.29</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -615,6 +615,39 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>inch built-in electric</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>$208.15</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -648,6 +648,39 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>monarch binocular high-magnification</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>$323.05</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -681,6 +681,39 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>thinkpad gen ai</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>$1145.07</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -714,6 +714,39 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>pad incline handle</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>$68.32</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -747,6 +747,39 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>air riders nintendo</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>$68.32</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -780,6 +780,39 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>prime power bank</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>$56.19</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -813,6 +813,39 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>makers countertop lbs</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>$1252.71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -846,6 +846,39 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>washer dryer pedestals</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>$147.95</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -879,6 +879,39 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>portable washing machine</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>$100.87</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -912,6 +912,39 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>portable countertop ice</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>$49.39</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -945,6 +945,39 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>tcg mega charizard</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>$85.83</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -978,6 +978,39 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>zulu hdx marine</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>$592.03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>69.2%</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1011,6 +1011,39 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>dock mk audio</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>$178.96</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1044,6 +1044,39 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>pad treadmill handle</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>$65.97</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>77.3%</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1077,6 +1077,39 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>electric bike adultsteens</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>$155.49</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1110,6 +1110,39 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>portable ice makers</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>$78.80</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,39 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>edition playstation</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>$117.32</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1176,39 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>note ai voice</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>$99.98</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>95.0%</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1209,6 +1209,39 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>minds strikepack horizon</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>$69.99</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1242,6 +1242,39 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>sealer machine kpa</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>$58.18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1275,6 +1275,39 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ice maker machine</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>$118.15</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1308,6 +1308,39 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>electric baby bassinet</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>$201.54</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>51.3%</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1341,6 +1341,39 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>snap selfie screen</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>$49.32</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1374,6 +1374,39 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ice makers countertop</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>$79.99</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1407,6 +1407,39 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>refrigerator ice maker</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>$76.20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>94.4%</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1440,6 +1440,39 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>portable range hood</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>$88.58</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1473,6 +1473,39 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>treadmills home foldable</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>$189.30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1506,6 +1506,39 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>vx left dash</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>$229.95</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1539,6 +1539,39 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ft patio umbrella</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>$61.61</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1572,6 +1572,39 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>high powered binoculars</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>$75.73</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1605,6 +1605,39 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>portable washer dryer</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>$113.06</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1638,6 +1638,39 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>xxft pcs galvanized</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>$160.47</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-14.xlsx
+++ b/output/amazon_niche_rapor_2026-04-14.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1671,6 +1671,39 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>gpm cordless fuel</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>$142.21</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>86.4%</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
